--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N70_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N70_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.1783606919297</v>
+        <v>9.778983612438577</v>
       </c>
       <c r="D2" t="n">
-        <v>48.12862947400877</v>
+        <v>7.820902289526425</v>
       </c>
       <c r="E2" t="n">
-        <v>8.360603632488827</v>
+        <v>1.358598090279434</v>
       </c>
       <c r="F2" t="n">
-        <v>11.99137917994494</v>
+        <v>1.948599116741053</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>50.26192938729563</v>
+        <v>8.16756352543554</v>
       </c>
       <c r="D3" t="n">
-        <v>39.04964179550041</v>
+        <v>6.345566791768817</v>
       </c>
       <c r="E3" t="n">
-        <v>8.360603632488827</v>
+        <v>1.358598090279434</v>
       </c>
       <c r="F3" t="n">
-        <v>11.99137917994494</v>
+        <v>1.948599116741053</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>54.1684113607228</v>
+        <v>8.802366846117454</v>
       </c>
       <c r="D4" t="n">
-        <v>17.57927026034573</v>
+        <v>2.856631417306182</v>
       </c>
       <c r="E4" t="n">
-        <v>8.360603632488827</v>
+        <v>1.358598090279434</v>
       </c>
       <c r="F4" t="n">
-        <v>11.99137917994494</v>
+        <v>1.948599116741053</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>43.70387918253763</v>
+        <v>7.101880367162365</v>
       </c>
       <c r="D5" t="n">
-        <v>35.66002305362487</v>
+        <v>5.794753746214042</v>
       </c>
       <c r="E5" t="n">
-        <v>8.360603632488827</v>
+        <v>1.358598090279434</v>
       </c>
       <c r="F5" t="n">
-        <v>11.99137917994494</v>
+        <v>1.948599116741053</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>62.50723574106043</v>
+        <v>10.15742580792232</v>
       </c>
       <c r="D6" t="n">
-        <v>49.16651580683266</v>
+        <v>7.989558818610307</v>
       </c>
       <c r="E6" t="n">
-        <v>8.360603632488827</v>
+        <v>1.358598090279434</v>
       </c>
       <c r="F6" t="n">
-        <v>11.99137917994494</v>
+        <v>1.948599116741053</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>51.72042432361692</v>
+        <v>8.40456895258775</v>
       </c>
       <c r="D7" t="n">
-        <v>38.20137173252477</v>
+        <v>6.207722906535276</v>
       </c>
       <c r="E7" t="n">
-        <v>8.360603632488827</v>
+        <v>1.358598090279434</v>
       </c>
       <c r="F7" t="n">
-        <v>11.99137917994494</v>
+        <v>1.948599116741053</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>39.74866317915017</v>
+        <v>6.459157766611903</v>
       </c>
       <c r="D8" t="n">
-        <v>30.33556178821435</v>
+        <v>4.929528790584832</v>
       </c>
       <c r="E8" t="n">
-        <v>8.360603632488827</v>
+        <v>1.358598090279434</v>
       </c>
       <c r="F8" t="n">
-        <v>11.99137917994494</v>
+        <v>1.948599116741053</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>40.14016266586852</v>
+        <v>6.522776433203635</v>
       </c>
       <c r="D9" t="n">
-        <v>27.80893588905999</v>
+        <v>4.518952081972249</v>
       </c>
       <c r="E9" t="n">
-        <v>8.360603632488827</v>
+        <v>1.358598090279434</v>
       </c>
       <c r="F9" t="n">
-        <v>11.99137917994494</v>
+        <v>1.948599116741053</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>62.97377909710338</v>
+        <v>10.2332391032793</v>
       </c>
       <c r="D10" t="n">
-        <v>50.29028485666483</v>
+        <v>8.172171289208034</v>
       </c>
       <c r="E10" t="n">
-        <v>8.360603632488827</v>
+        <v>1.358598090279434</v>
       </c>
       <c r="F10" t="n">
-        <v>11.99137917994494</v>
+        <v>1.948599116741053</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>40.61949762992685</v>
+        <v>6.600668364863114</v>
       </c>
       <c r="D11" t="n">
-        <v>14.46468621472891</v>
+        <v>2.350511509893448</v>
       </c>
       <c r="E11" t="n">
-        <v>8.360603632488827</v>
+        <v>1.358598090279434</v>
       </c>
       <c r="F11" t="n">
-        <v>11.99137917994494</v>
+        <v>1.948599116741053</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>58.52750177889119</v>
+        <v>9.510719039069819</v>
       </c>
       <c r="D12" t="n">
-        <v>47.49508573985258</v>
+        <v>7.717951432726044</v>
       </c>
       <c r="E12" t="n">
-        <v>8.360603632488827</v>
+        <v>1.358598090279434</v>
       </c>
       <c r="F12" t="n">
-        <v>11.99137917994494</v>
+        <v>1.948599116741053</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>42.38057084791842</v>
+        <v>6.886842762786744</v>
       </c>
       <c r="D13" t="n">
-        <v>38.53112918429758</v>
+        <v>6.261308492448357</v>
       </c>
       <c r="E13" t="n">
-        <v>8.360603632488827</v>
+        <v>1.358598090279434</v>
       </c>
       <c r="F13" t="n">
-        <v>11.99137917994494</v>
+        <v>1.948599116741053</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>48.70684730361516</v>
+        <v>7.914862686837463</v>
       </c>
       <c r="D14" t="n">
-        <v>18.62481498601628</v>
+        <v>3.026532435227645</v>
       </c>
       <c r="E14" t="n">
-        <v>8.360603632488827</v>
+        <v>1.358598090279434</v>
       </c>
       <c r="F14" t="n">
-        <v>11.99137917994494</v>
+        <v>1.948599116741053</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
